--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487945_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487945_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3464</v>
+        <v>4.2726</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4362</v>
+        <v>3.3344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9101</v>
+        <v>0.9382</v>
       </c>
       <c r="G2" t="n">
         <v>4.1213</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2309</v>
+        <v>-0.3047</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1286</v>
+        <v>0.0267</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3595</v>
+        <v>-0.3314</v>
       </c>
       <c r="V2" t="n">
         <v>-0.337</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>D. GUAITA MACHADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7737</v>
+        <v>3.1437</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3937</v>
+        <v>1.8612</v>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.2825</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3123</v>
+        <v>1.8571</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0394</v>
+        <v>1.2047</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7271</v>
+        <v>0.6524</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6849</v>
+        <v>2.8728</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9578</v>
+        <v>1.0492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7271</v>
+        <v>1.8236</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3725</v>
+        <v>-1.0157</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.1554</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4542</v>
+        <v>-1.1711</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1805</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5891</v>
+        <v>-0.1276</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4244</v>
+        <v>-0.1155</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1647</v>
+        <v>-0.0122</v>
       </c>
       <c r="V3" t="n">
-        <v>0.674</v>
+        <v>1.8107</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2666</v>
+        <v>2.0772</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4074</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3646</v>
+        <v>2.993</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8712</v>
+        <v>1.6411</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4934</v>
+        <v>1.3519</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6782</v>
+        <v>1.3123</v>
       </c>
       <c r="H4" t="n">
-        <v>3.691</v>
+        <v>2.0394</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0128</v>
+        <v>-0.7271</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3224</v>
+        <v>2.6849</v>
       </c>
       <c r="K4" t="n">
-        <v>3.881</v>
+        <v>1.9578</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5586</v>
+        <v>0.7271</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6442</v>
+        <v>-1.3725</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.19</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>-1.4542</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4198</v>
+        <v>0.8085</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2644</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1553</v>
+        <v>0.1366</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2666</v>
+        <v>0.674</v>
       </c>
       <c r="W4" t="n">
         <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GUAITA MACHADO</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2174</v>
+        <v>2.6055</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1876</v>
+        <v>1.7298</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0298</v>
+        <v>0.8757</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8571</v>
+        <v>1.6782</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2047</v>
+        <v>3.691</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6524</v>
+        <v>-2.0128</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8728</v>
+        <v>3.3224</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0492</v>
+        <v>3.881</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8236</v>
+        <v>-0.5586</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0157</v>
+        <v>-1.6442</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1554</v>
+        <v>-0.19</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1711</v>
+        <v>-1.4542</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5769</v>
+        <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.054</v>
+        <v>0.6607</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7891</v>
+        <v>0.1231</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2649</v>
+        <v>0.5376</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8107</v>
+        <v>0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0772</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4443</v>
+        <v>2.3458</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8439</v>
+        <v>3.2119</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3996</v>
+        <v>-0.8661</v>
       </c>
       <c r="G6" t="n">
         <v>4.045</v>
@@ -922,13 +922,13 @@
         <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4797</v>
+        <v>-0.5782</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.121</v>
+        <v>0.247</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3587</v>
+        <v>-0.8252</v>
       </c>
       <c r="V6" t="n">
         <v>0.2666</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1593</v>
+        <v>1.4557</v>
       </c>
       <c r="E7" t="n">
-        <v>2.095</v>
+        <v>1.3025</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9357</v>
+        <v>0.1532</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7902</v>
+        <v>2.4334</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9006</v>
+        <v>1.4902</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.9433</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2783</v>
+        <v>3.9265</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5473</v>
+        <v>1.5404</v>
       </c>
       <c r="L7" t="n">
-        <v>0.731</v>
+        <v>2.386</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5119</v>
+        <v>-1.493</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3533</v>
+        <v>-0.0503</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1586</v>
+        <v>-1.4428</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2673</v>
+        <v>0.0311</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4223</v>
+        <v>0.0322</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6896</v>
+        <v>-0.0011</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7512</v>
+        <v>-1.2071</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4074</v>
+        <v>-0.674</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3438</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8558</v>
+        <v>0.8328</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7308</v>
+        <v>1.9931</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1251</v>
+        <v>-1.1603</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4334</v>
+        <v>2.7902</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4902</v>
+        <v>1.9006</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9433</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9265</v>
+        <v>2.2783</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5404</v>
+        <v>1.5473</v>
       </c>
       <c r="L8" t="n">
-        <v>2.386</v>
+        <v>0.731</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.493</v>
+        <v>0.5119</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0503</v>
+        <v>0.3533</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4428</v>
+        <v>0.1586</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-0.1982</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5687</v>
+        <v>-0.5938</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5395</v>
+        <v>0.3204</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0292</v>
+        <v>-0.9142</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2071</v>
+        <v>-2.7512</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.674</v>
+        <v>-0.4074</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5331</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>D. GUERRERO JONSSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1686</v>
+        <v>0.0284</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9937</v>
+        <v>-0.9868</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1623</v>
+        <v>1.0152</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3793</v>
+        <v>-0.3028</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8824</v>
+        <v>-0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5031</v>
+        <v>0.0402</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3697</v>
+        <v>-0.5784</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2692</v>
+        <v>-0.6186</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.639</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>0.749</v>
+        <v>0.2756</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6132</v>
+        <v>0.2756</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1358</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1857</v>
+        <v>-0.2634</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3671</v>
+        <v>-0.2101</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1814</v>
+        <v>-0.0533</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GUERRERO JONSSON</t>
+          <t>M. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1296</v>
+        <v>-0.1289</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0886</v>
+        <v>1.5332</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9591</v>
+        <v>-1.662</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3028</v>
+        <v>0.1294</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.343</v>
+        <v>-0.0217</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0402</v>
+        <v>0.1511</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5784</v>
+        <v>0.0442</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6186</v>
+        <v>0.0404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>0.0039</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2756</v>
+        <v>0.0852</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2756</v>
+        <v>-0.062</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="P10" t="n">
         <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4214</v>
+        <v>-0.5864</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>0.2818</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1094</v>
+        <v>-0.8682</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LIBERATORE DARGAM</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2869</v>
+        <v>-0.3512</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4313</v>
+        <v>-1.4012</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7182</v>
+        <v>1.05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1294</v>
+        <v>0.3793</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0217</v>
+        <v>0.8824</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1511</v>
+        <v>-0.5031</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0442</v>
+        <v>-0.3697</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0404</v>
+        <v>0.2692</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0039</v>
+        <v>-0.639</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0852</v>
+        <v>0.749</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.062</v>
+        <v>0.6132</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1472</v>
+        <v>0.1358</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
         <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7444</v>
+        <v>-0.334</v>
       </c>
       <c r="T11" t="n">
-        <v>0.18</v>
+        <v>-0.0403</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9244</v>
+        <v>-0.2937</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6968</v>
+        <v>-1.3912</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5777</v>
+        <v>-0.2721</v>
       </c>
       <c r="F12" t="n">
         <v>-1.1191</v>
@@ -1390,10 +1390,10 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8905</v>
+        <v>-1.5849</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4881</v>
+        <v>-0.1825</v>
       </c>
       <c r="U12" t="n">
         <v>-1.4024</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5865</v>
+        <v>-3.864</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0421</v>
+        <v>-4.3477</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4556</v>
+        <v>0.4837</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2992</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6355</v>
+        <v>0.3579</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8591</v>
+        <v>0.5535</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2236</v>
+        <v>-0.1956</v>
       </c>
       <c r="V13" t="n">
         <v>-0.337</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.6303</v>
+        <v>11.9422</v>
       </c>
       <c r="E14" t="n">
-        <v>9.287600000000001</v>
+        <v>9.599400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3428</v>
+        <v>2.3429</v>
       </c>
       <c r="G14" t="n">
         <v>15.88</v>
@@ -1528,7 +1528,7 @@
         <v>7.864599999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.661199999999999</v>
+        <v>-5.661200000000001</v>
       </c>
       <c r="N14" t="n">
         <v>0.8164</v>
@@ -1546,13 +1546,13 @@
         <v>17.8402</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8268</v>
+        <v>-2.514800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3962</v>
+        <v>1.7082</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.223100000000001</v>
+        <v>-4.2231</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4141</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6817</v>
+        <v>3.8769</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2029</v>
+        <v>3.8973</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5212</v>
+        <v>-0.0203</v>
       </c>
       <c r="G15" t="n">
         <v>1.303</v>
@@ -1624,13 +1624,13 @@
         <v>1.5858</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3609</v>
+        <v>0.5561</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2373</v>
+        <v>0.9316</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8764</v>
+        <v>-0.3755</v>
       </c>
       <c r="V15" t="n">
         <v>2.4142</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1627</v>
+        <v>2.9054</v>
       </c>
       <c r="E16" t="n">
         <v>2.3403</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8224</v>
+        <v>0.5651</v>
       </c>
       <c r="G16" t="n">
         <v>0.9792999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>1.331</v>
+        <v>1.0737</v>
       </c>
       <c r="T16" t="n">
         <v>0.9215</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4095</v>
+        <v>0.1522</v>
       </c>
       <c r="V16" t="n">
         <v>-0.337</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.407</v>
+        <v>0.4596</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2908</v>
+        <v>0.0542</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6979</v>
+        <v>0.4054</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9457</v>
+        <v>-0.6007</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4872</v>
+        <v>-1.5955</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5415</v>
+        <v>0.9949</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5298</v>
+        <v>0.7754</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7944</v>
+        <v>-1.2775</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7354</v>
+        <v>2.053</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4755</v>
+        <v>-1.3761</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2816</v>
+        <v>-0.318</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1939</v>
+        <v>-1.0581</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3821</v>
+        <v>-0.0101</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.444</v>
+        <v>0.2699</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0619</v>
+        <v>-0.28</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0704</v>
+        <v>0.674</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERRERA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7907</v>
+        <v>0.0063</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1872</v>
+        <v>1.5965</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6036</v>
+        <v>-1.5901</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6036</v>
+        <v>-0.9457</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2018</v>
+        <v>-1.4872</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4018</v>
+        <v>0.5415</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.5298</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.7944</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.7354</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6036</v>
+        <v>-3.4755</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2018</v>
+        <v>-2.2816</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4018</v>
+        <v>-1.1939</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1872</v>
+        <v>0.0313</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1872</v>
+        <v>-0.1384</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.1697</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8052</v>
+        <v>-0.7907</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5777</v>
+        <v>-0.1872</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2275</v>
+        <v>-0.6036</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3208</v>
+        <v>-0.6036</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.7117</v>
+        <v>-0.2018</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3909</v>
+        <v>-0.4018</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5376</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2323</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6947</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7832</v>
+        <v>-0.6036</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4794</v>
+        <v>-0.2018</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6962</v>
+        <v>-0.4018</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5443</v>
+        <v>-0.1872</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0412</v>
+        <v>-0.1872</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5031</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6145</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.0813</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0599</v>
+        <v>-1.0281</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9645</v>
+        <v>-1.1387</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0954</v>
+        <v>0.1106</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6007</v>
+        <v>-4.5949</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5955</v>
+        <v>-1.8859</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9949</v>
+        <v>-2.709</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7754</v>
+        <v>-2.468</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2775</v>
+        <v>0.128</v>
       </c>
       <c r="L20" t="n">
-        <v>2.053</v>
+        <v>-2.596</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3761</v>
+        <v>-2.1269</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.318</v>
+        <v>-2.0138</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0581</v>
+        <v>-0.113</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5296</v>
+        <v>0.2386</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7488</v>
+        <v>0.1222</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7809</v>
+        <v>0.1164</v>
       </c>
       <c r="V20" t="n">
-        <v>0.674</v>
+        <v>1.5441</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X20" t="n">
-        <v>0.674</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3853</v>
+        <v>-1.126</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4443</v>
+        <v>-1.083</v>
       </c>
       <c r="F21" t="n">
-        <v>0.059</v>
+        <v>-0.043</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5949</v>
+        <v>-0.9272</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8859</v>
+        <v>0.1747</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.709</v>
+        <v>-1.1019</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.468</v>
+        <v>0.0453</v>
       </c>
       <c r="K21" t="n">
-        <v>0.128</v>
+        <v>0.6324</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.596</v>
+        <v>-0.5871</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1269</v>
+        <v>-0.9725</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0138</v>
+        <v>-0.4577</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.113</v>
+        <v>-0.5148</v>
       </c>
       <c r="P21" t="n">
-        <v>1.784</v>
+        <v>-1.784</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1186</v>
+        <v>0.3781</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1834</v>
+        <v>0.6379</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0648</v>
+        <v>-0.2598</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5441</v>
+        <v>1.2071</v>
       </c>
       <c r="W21" t="n">
         <v>1.2071</v>
       </c>
       <c r="X21" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7196</v>
+        <v>-2.3483</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5923</v>
+        <v>-2.0039</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1273</v>
+        <v>-0.3444</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9272</v>
+        <v>-3.3208</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1747</v>
+        <v>-4.7117</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1019</v>
+        <v>1.3909</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0453</v>
+        <v>-1.5376</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6324</v>
+        <v>-2.2323</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5871</v>
+        <v>0.6947</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9725</v>
+        <v>-1.7832</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4577</v>
+        <v>-2.4794</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5148</v>
+        <v>0.6962</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2155</v>
+        <v>1.0012</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1286</v>
+        <v>0.615</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3441</v>
+        <v>0.3862</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2071</v>
+        <v>-1.6145</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2071</v>
+        <v>-1.0813</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0617</v>
+        <v>-3.4304</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1889</v>
+        <v>-1.3391</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2506</v>
+        <v>-2.0912</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2466</v>
@@ -2248,13 +2248,13 @@
         <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5903</v>
+        <v>1.2216</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9516</v>
+        <v>1.4236</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3614</v>
+        <v>-0.202</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9866</v>
+        <v>-3.8671</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3737</v>
+        <v>-1.1699</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6129</v>
+        <v>-2.6972</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2835</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1699</v>
+        <v>-0.0504</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3706</v>
+        <v>-0.1669</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2007</v>
+        <v>0.1164</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7403</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2585</v>
+        <v>-4.9296</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.226</v>
+        <v>-3.3092</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0325</v>
+        <v>-1.6204</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6396</v>
@@ -2404,13 +2404,13 @@
         <v>2.1805</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3967</v>
+        <v>-0.0678</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1232</v>
+        <v>-0.2063</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2735</v>
+        <v>0.1385</v>
       </c>
       <c r="V25" t="n">
         <v>1.5441</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.6301</v>
+        <v>-10.272</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3428</v>
+        <v>-2.342699999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.2875</v>
+        <v>-7.9291</v>
       </c>
       <c r="G26" t="n">
         <v>-15.8803</v>
@@ -2455,13 +2455,13 @@
         <v>-1.3868</v>
       </c>
       <c r="J26" t="n">
-        <v>5.661300000000001</v>
+        <v>5.6613</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.8165000000000004</v>
+        <v>-0.8164999999999996</v>
       </c>
       <c r="L26" t="n">
-        <v>6.477800000000001</v>
+        <v>6.477799999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-21.5415</v>
@@ -2482,13 +2482,13 @@
         <v>16.8489</v>
       </c>
       <c r="S26" t="n">
-        <v>2.826899999999999</v>
+        <v>4.1851</v>
       </c>
       <c r="T26" t="n">
-        <v>4.223000000000001</v>
+        <v>4.2229</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3963</v>
+        <v>-0.03789999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>2.4142</v>
